--- a/tiflow-xborder/main/2.0.0-ballot.2/StructureDefinition-GEM-ERPEU-PR-Medication.xlsx
+++ b/tiflow-xborder/main/2.0.0-ballot.2/StructureDefinition-GEM-ERPEU-PR-Medication.xlsx
@@ -650,6 +650,9 @@
 </t>
   </si>
   <si>
+    <t>Extension</t>
+  </si>
+  <si>
     <t>This extension is used to track medication prescription transactions between the E-Rezept-Fachdienst and the ePA. The RxPrescriptionProcessIdentifier is generated by the ePA Medication Service and consists of the PrescriptionId and the authoredOn date of the operation parameters request. It ensures consistent referencing and management of medication-related resources across different systems.</t>
   </si>
   <si>
@@ -933,9 +936,6 @@
   <si>
     <t xml:space="preserve">Extension {https://gematik.de/fhir/epa-medication/StructureDefinition/medication-manufacturing-instructions-extension}
 </t>
-  </si>
-  <si>
-    <t>Extension</t>
   </si>
   <si>
     <t>Manufacturing instructions regarding the preparation of a formulation (Subscriptio).</t>
@@ -4638,10 +4638,10 @@
         <v>200</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>111</v>
@@ -4712,7 +4712,7 @@
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>105</v>
+        <v>189</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -4723,13 +4723,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>190</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>107</v>
@@ -4751,13 +4751,13 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L20" t="s" s="2">
         <v>196</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>111</v>
@@ -4839,13 +4839,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>190</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>107</v>
@@ -4867,13 +4867,13 @@
         <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>196</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>111</v>
@@ -4955,10 +4955,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5067,10 +5067,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5181,10 +5181,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5210,13 +5210,13 @@
         <v>129</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>77</v>
@@ -5266,7 +5266,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>87</v>
@@ -5295,10 +5295,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5324,10 +5324,10 @@
         <v>141</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -5354,11 +5354,11 @@
         <v>77</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>77</v>
@@ -5376,7 +5376,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -5405,10 +5405,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5517,10 +5517,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5631,10 +5631,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5660,16 +5660,16 @@
         <v>129</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -5718,7 +5718,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5736,21 +5736,21 @@
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5776,13 +5776,13 @@
         <v>101</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5832,7 +5832,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5850,21 +5850,21 @@
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5890,14 +5890,14 @@
         <v>166</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -5946,7 +5946,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5964,21 +5964,21 @@
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6004,16 +6004,16 @@
         <v>101</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -6062,7 +6062,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -6080,21 +6080,21 @@
         <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6117,19 +6117,19 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>77</v>
@@ -6178,7 +6178,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -6196,24 +6196,24 @@
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>190</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>107</v>
@@ -6235,13 +6235,13 @@
         <v>77</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>111</v>
@@ -6323,10 +6323,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6435,10 +6435,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6549,10 +6549,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6578,13 +6578,13 @@
         <v>129</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6592,7 +6592,7 @@
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>77</v>
@@ -6634,7 +6634,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>87</v>
@@ -6663,10 +6663,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6692,10 +6692,10 @@
         <v>166</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6722,11 +6722,11 @@
         <v>77</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Y37" s="2"/>
       <c r="Z37" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>77</v>
@@ -6744,7 +6744,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6773,13 +6773,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>190</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>107</v>
@@ -6801,13 +6801,13 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L38" t="s" s="2">
         <v>196</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N38" t="s" s="2">
         <v>111</v>
@@ -6889,13 +6889,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>190</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>107</v>
@@ -6917,10 +6917,10 @@
         <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>294</v>
+        <v>201</v>
       </c>
       <c r="M39" t="s" s="2">
         <v>295</v>
@@ -7152,7 +7152,7 @@
         <v>303</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>294</v>
+        <v>201</v>
       </c>
       <c r="M41" t="s" s="2">
         <v>304</v>
@@ -7266,7 +7266,7 @@
         <v>307</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>294</v>
+        <v>201</v>
       </c>
       <c r="M42" t="s" s="2">
         <v>304</v>
@@ -8636,16 +8636,16 @@
         <v>129</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -8694,7 +8694,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8712,13 +8712,13 @@
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="55" hidden="true">
@@ -8752,13 +8752,13 @@
         <v>101</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8808,7 +8808,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8826,13 +8826,13 @@
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="56">
@@ -8873,7 +8873,7 @@
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>77</v>
@@ -8922,7 +8922,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8940,13 +8940,13 @@
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="57">
@@ -8980,16 +8980,16 @@
         <v>101</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>77</v>
@@ -9038,7 +9038,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -9056,13 +9056,13 @@
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="58" hidden="true">
@@ -9093,19 +9093,19 @@
         <v>88</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>77</v>
@@ -9154,7 +9154,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -9172,13 +9172,13 @@
         <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="59">
@@ -9556,16 +9556,16 @@
         <v>129</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>77</v>
@@ -9614,7 +9614,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9632,13 +9632,13 @@
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="63" hidden="true">
@@ -9672,13 +9672,13 @@
         <v>101</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9728,7 +9728,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9746,13 +9746,13 @@
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="64">
@@ -9793,7 +9793,7 @@
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>77</v>
@@ -9842,7 +9842,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9860,13 +9860,13 @@
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="65">
@@ -9900,16 +9900,16 @@
         <v>101</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -9958,7 +9958,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9976,13 +9976,13 @@
         <v>77</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="66" hidden="true">
@@ -10013,19 +10013,19 @@
         <v>88</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>77</v>
@@ -10074,7 +10074,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -10092,13 +10092,13 @@
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="67">
@@ -10476,16 +10476,16 @@
         <v>129</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>77</v>
@@ -10534,7 +10534,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10552,13 +10552,13 @@
         <v>77</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="71" hidden="true">
@@ -10592,13 +10592,13 @@
         <v>101</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10648,7 +10648,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10666,13 +10666,13 @@
         <v>77</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="72">
@@ -10713,7 +10713,7 @@
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>77</v>
@@ -10762,7 +10762,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10780,13 +10780,13 @@
         <v>77</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="73">
@@ -10820,16 +10820,16 @@
         <v>101</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>77</v>
@@ -10878,7 +10878,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10896,13 +10896,13 @@
         <v>77</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="74" hidden="true">
@@ -10933,19 +10933,19 @@
         <v>88</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>77</v>
@@ -10994,7 +10994,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -11012,13 +11012,13 @@
         <v>77</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="75">
@@ -11200,7 +11200,7 @@
         <v>77</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Y76" t="s" s="2">
         <v>404</v>
@@ -12684,7 +12684,7 @@
         <v>77</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Y89" s="2"/>
       <c r="Z89" t="s" s="2">
@@ -12990,16 +12990,16 @@
         <v>129</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>77</v>
@@ -13048,7 +13048,7 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13066,13 +13066,13 @@
         <v>77</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="93" hidden="true">
@@ -13106,13 +13106,13 @@
         <v>101</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13162,7 +13162,7 @@
         <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13180,13 +13180,13 @@
         <v>77</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="94">
@@ -13227,7 +13227,7 @@
       </c>
       <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>77</v>
@@ -13276,7 +13276,7 @@
         <v>77</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13294,13 +13294,13 @@
         <v>77</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="95">
@@ -13334,16 +13334,16 @@
         <v>101</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>77</v>
@@ -13392,7 +13392,7 @@
         <v>77</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13410,13 +13410,13 @@
         <v>77</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="96" hidden="true">
@@ -13447,19 +13447,19 @@
         <v>88</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>77</v>
@@ -13508,7 +13508,7 @@
         <v>77</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13526,13 +13526,13 @@
         <v>77</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="97">
@@ -13602,7 +13602,7 @@
         <v>77</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Y97" s="2"/>
       <c r="Z97" t="s" s="2">
@@ -13908,16 +13908,16 @@
         <v>129</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>77</v>
@@ -13966,7 +13966,7 @@
         <v>77</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -13984,13 +13984,13 @@
         <v>77</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="101" hidden="true">
@@ -14024,13 +14024,13 @@
         <v>101</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14080,7 +14080,7 @@
         <v>77</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -14098,13 +14098,13 @@
         <v>77</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="102">
@@ -14145,7 +14145,7 @@
       </c>
       <c r="N102" s="2"/>
       <c r="O102" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>77</v>
@@ -14194,7 +14194,7 @@
         <v>77</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -14212,13 +14212,13 @@
         <v>77</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="103">
@@ -14252,16 +14252,16 @@
         <v>101</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>77</v>
@@ -14310,7 +14310,7 @@
         <v>77</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -14328,13 +14328,13 @@
         <v>77</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="104" hidden="true">
@@ -14365,19 +14365,19 @@
         <v>88</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>77</v>
@@ -14426,7 +14426,7 @@
         <v>77</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -14444,13 +14444,13 @@
         <v>77</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="105">
@@ -15660,7 +15660,7 @@
         <v>77</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Y115" t="s" s="2">
         <v>535</v>
@@ -15748,7 +15748,7 @@
         <v>542</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O116" t="s" s="2">
         <v>543</v>
@@ -16578,7 +16578,7 @@
         <v>77</v>
       </c>
       <c r="X123" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Y123" t="s" s="2">
         <v>535</v>
@@ -16666,7 +16666,7 @@
         <v>542</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O124" t="s" s="2">
         <v>543</v>
@@ -18492,16 +18492,16 @@
         <v>129</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>77</v>
@@ -18550,7 +18550,7 @@
         <v>77</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>78</v>
@@ -18568,13 +18568,13 @@
         <v>77</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AM140" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="141" hidden="true">
@@ -18608,13 +18608,13 @@
         <v>101</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -18664,7 +18664,7 @@
         <v>77</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>78</v>
@@ -18682,13 +18682,13 @@
         <v>77</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AM141" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="142">
@@ -18729,7 +18729,7 @@
       </c>
       <c r="N142" s="2"/>
       <c r="O142" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>77</v>
@@ -18778,7 +18778,7 @@
         <v>77</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>78</v>
@@ -18796,13 +18796,13 @@
         <v>77</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AM142" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="143">
@@ -18836,16 +18836,16 @@
         <v>101</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>77</v>
@@ -18894,7 +18894,7 @@
         <v>77</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>78</v>
@@ -18912,13 +18912,13 @@
         <v>77</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AM143" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="144" hidden="true">
@@ -18949,19 +18949,19 @@
         <v>88</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O144" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>77</v>
@@ -19010,7 +19010,7 @@
         <v>77</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>78</v>
@@ -19028,13 +19028,13 @@
         <v>77</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AM144" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="145">
@@ -19412,16 +19412,16 @@
         <v>129</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>77</v>
@@ -19470,7 +19470,7 @@
         <v>77</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>78</v>
@@ -19488,13 +19488,13 @@
         <v>77</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AM148" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="149" hidden="true">
@@ -19528,13 +19528,13 @@
         <v>101</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -19584,7 +19584,7 @@
         <v>77</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>78</v>
@@ -19602,13 +19602,13 @@
         <v>77</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AM149" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="150">
@@ -19649,7 +19649,7 @@
       </c>
       <c r="N150" s="2"/>
       <c r="O150" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>77</v>
@@ -19698,7 +19698,7 @@
         <v>77</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>78</v>
@@ -19716,13 +19716,13 @@
         <v>77</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AM150" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="151">
@@ -19756,16 +19756,16 @@
         <v>101</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>77</v>
@@ -19814,7 +19814,7 @@
         <v>77</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>78</v>
@@ -19832,13 +19832,13 @@
         <v>77</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AM151" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="152" hidden="true">
@@ -19869,19 +19869,19 @@
         <v>88</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O152" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>77</v>
@@ -19930,7 +19930,7 @@
         <v>77</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>78</v>
@@ -19948,13 +19948,13 @@
         <v>77</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AM152" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="153">
@@ -20332,16 +20332,16 @@
         <v>129</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>77</v>
@@ -20390,7 +20390,7 @@
         <v>77</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>78</v>
@@ -20408,13 +20408,13 @@
         <v>77</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AM156" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="157" hidden="true">
@@ -20448,13 +20448,13 @@
         <v>101</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
@@ -20504,7 +20504,7 @@
         <v>77</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>78</v>
@@ -20522,13 +20522,13 @@
         <v>77</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AM157" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="158">
@@ -20569,7 +20569,7 @@
       </c>
       <c r="N158" s="2"/>
       <c r="O158" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>77</v>
@@ -20618,7 +20618,7 @@
         <v>77</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>78</v>
@@ -20636,13 +20636,13 @@
         <v>77</v>
       </c>
       <c r="AL158" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AM158" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN158" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="159">
@@ -20676,16 +20676,16 @@
         <v>101</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>77</v>
@@ -20734,7 +20734,7 @@
         <v>77</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>78</v>
@@ -20752,13 +20752,13 @@
         <v>77</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AM159" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="160" hidden="true">
@@ -20789,19 +20789,19 @@
         <v>88</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O160" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>77</v>
@@ -20850,7 +20850,7 @@
         <v>77</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>78</v>
@@ -20868,13 +20868,13 @@
         <v>77</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AM160" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN160" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="161">
@@ -21137,7 +21137,7 @@
         <v>77</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L163" t="s" s="2">
         <v>646</v>
@@ -22198,7 +22198,7 @@
         <v>77</v>
       </c>
       <c r="X172" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Y172" t="s" s="2">
         <v>535</v>
@@ -22286,7 +22286,7 @@
         <v>542</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O173" t="s" s="2">
         <v>543</v>
@@ -23116,7 +23116,7 @@
         <v>77</v>
       </c>
       <c r="X180" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Y180" t="s" s="2">
         <v>535</v>
@@ -23204,7 +23204,7 @@
         <v>542</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O181" t="s" s="2">
         <v>543</v>
@@ -24006,7 +24006,7 @@
         <v>686</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O188" s="2"/>
       <c r="P188" t="s" s="2">
